--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B5" t="n">
-        <v>57967</v>
+        <v>58055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R5" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>57967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R6" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128507091</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>58055</v>
+        <v>57971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R5" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>57967</v>
+        <v>58059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R6" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B5" t="n">
-        <v>57971</v>
+        <v>58059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R5" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B6" t="n">
-        <v>58059</v>
+        <v>57971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R6" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>58059</v>
+        <v>57971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R5" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>57971</v>
+        <v>58059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R6" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128507091</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>57971</v>
+        <v>57998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128507091</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>57998</v>
+        <v>58002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B5" t="n">
-        <v>58002</v>
+        <v>58090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R5" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>58002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R6" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>58090</v>
+        <v>58002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R5" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>58002</v>
+        <v>58090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R6" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128507091</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>58002</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128507052</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R5" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B6" t="n">
-        <v>58093</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R6" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34935-2025 artfynd.xlsx
+++ b/artfynd/A 34935-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128550042</v>
+        <v>128550045</v>
       </c>
       <c r="B5" t="n">
-        <v>58093</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585306</v>
+        <v>585356</v>
       </c>
       <c r="R5" t="n">
-        <v>6317581</v>
+        <v>6317580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1120,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128550045</v>
+        <v>128550042</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585356</v>
+        <v>585306</v>
       </c>
       <c r="R6" t="n">
-        <v>6317580</v>
+        <v>6317581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
